--- a/Documentation/Product Backlog.xlsx
+++ b/Documentation/Product Backlog.xlsx
@@ -10,14 +10,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="dlJSTRlvYHWG3YC1wSlTltRlUt4ipLnyD75J993mBxk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="3PBw/UMHYqlYPhKzsanCSHbSuuhAOt+TGHgKSKTBL+0="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t xml:space="preserve">    </t>
   </si>
@@ -71,7 +71,7 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Por hacer</t>
+    <t>Hecho</t>
   </si>
   <si>
     <t>HU-09</t>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Script de Backup</t>
+  </si>
+  <si>
+    <t>H-10</t>
+  </si>
+  <si>
+    <t>Proyecto en Figma</t>
   </si>
   <si>
     <t>HU-01</t>
@@ -188,6 +194,28 @@
     <t>EPICA 5: UX/UI</t>
   </si>
   <si>
+    <t>HU-11</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="10.0"/>
+      </rPr>
+      <t xml:space="preserve">Consumo de API </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF1155CC"/>
+        <sz val="10.0"/>
+        <u/>
+      </rPr>
+      <t>Mindicador.cl</t>
+    </r>
+  </si>
+  <si>
     <t>https://www.appvizer.es/revista/organizacion-planificacion/gestion-proyectos/planning-poker</t>
   </si>
 </sst>
@@ -195,7 +223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -230,6 +258,12 @@
       <name val="Arial"/>
     </font>
     <font/>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -470,8 +504,8 @@
     <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="8" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -488,13 +522,13 @@
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -509,13 +543,13 @@
     <xf borderId="14" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="14" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
@@ -760,7 +794,7 @@
     <xdr:ext cx="4048125" cy="3429000"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr descr="6 juegos de cartas de póker de estimación Agile con la serie Fibonacci :  Amazon.es: Juguetes y juegos" id="0" name="image2.jpg"/>
+        <xdr:cNvPr descr="6 juegos de cartas de póker de estimación Agile con la serie Fibonacci :  Amazon.es: Juguetes y juegos" id="0" name="image1.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -788,7 +822,7 @@
     <xdr:ext cx="6562725" cy="3962400"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png"/>
+        <xdr:cNvPr id="0" name="image2.png"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1012,7 +1046,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.57"/>
-    <col customWidth="1" min="2" max="2" width="45.0"/>
+    <col customWidth="1" min="2" max="2" width="0.43"/>
     <col customWidth="1" min="3" max="3" width="23.57"/>
     <col customWidth="1" min="4" max="4" width="23.86"/>
     <col customWidth="1" min="5" max="5" width="20.57"/>
@@ -1173,37 +1207,33 @@
       <c r="AA3" s="5"/>
     </row>
     <row r="4" ht="63.0" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>24</v>
+      <c r="E4" s="12"/>
+      <c r="F4" s="11">
+        <v>8.0</v>
       </c>
-      <c r="D4" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="18">
+      <c r="G4" s="11">
         <v>5.0</v>
       </c>
-      <c r="G4" s="18">
-        <v>3.0</v>
-      </c>
-      <c r="H4" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="I4" s="19">
+      <c r="H4" s="11">
         <v>1.0</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="I4" s="11">
+        <v>1.0</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L4" s="5"/>
@@ -1225,34 +1255,36 @@
     </row>
     <row r="5" ht="63.0" customHeight="1">
       <c r="A5" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="E5" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="20"/>
       <c r="F5" s="18">
         <v>5.0</v>
       </c>
       <c r="G5" s="18">
         <v>3.0</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="19">
         <v>2.0</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="19">
         <v>1.0</v>
       </c>
       <c r="J5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L5" s="5"/>
@@ -1272,38 +1304,36 @@
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
     </row>
-    <row r="6" ht="30.75" customHeight="1">
+    <row r="6" ht="63.0" customHeight="1">
       <c r="A6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>32</v>
+      <c r="E6" s="20"/>
+      <c r="F6" s="18">
+        <v>5.0</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="22">
+      <c r="G6" s="18">
         <v>3.0</v>
       </c>
-      <c r="G6" s="18">
+      <c r="H6" s="18">
         <v>2.0</v>
       </c>
-      <c r="H6" s="23">
-        <v>2.0</v>
-      </c>
-      <c r="I6" s="17">
+      <c r="I6" s="18">
         <v>1.0</v>
       </c>
-      <c r="J6" s="22" t="s">
-        <v>35</v>
+      <c r="J6" s="18" t="s">
+        <v>16</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L6" s="5"/>
@@ -1323,36 +1353,38 @@
       <c r="Z6" s="5"/>
       <c r="AA6" s="5"/>
     </row>
-    <row r="7" ht="39.0" customHeight="1">
+    <row r="7" ht="30.75" customHeight="1">
       <c r="A7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="24"/>
       <c r="F7" s="22">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G7" s="18">
-        <v>3.0</v>
-      </c>
-      <c r="H7" s="25">
         <v>2.0</v>
       </c>
-      <c r="I7" s="25">
+      <c r="H7" s="23">
+        <v>2.0</v>
+      </c>
+      <c r="I7" s="17">
         <v>1.0</v>
       </c>
       <c r="J7" s="22" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L7" s="5"/>
@@ -1372,36 +1404,36 @@
       <c r="Z7" s="5"/>
       <c r="AA7" s="5"/>
     </row>
-    <row r="8" ht="53.25" customHeight="1">
-      <c r="A8" s="14" t="s">
+    <row r="8" ht="39.0" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="20"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="22">
         <v>5.0</v>
       </c>
       <c r="G8" s="18">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H8" s="25">
         <v>2.0</v>
       </c>
       <c r="I8" s="25">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J8" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L8" s="5"/>
@@ -1422,26 +1454,24 @@
       <c r="AA8" s="5"/>
     </row>
     <row r="9" ht="53.25" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>32</v>
+      <c r="E9" s="20"/>
+      <c r="F9" s="22">
+        <v>5.0</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="22">
-        <v>8.0</v>
-      </c>
-      <c r="G9" s="19">
-        <v>5.0</v>
+      <c r="G9" s="18">
+        <v>2.0</v>
       </c>
       <c r="H9" s="25">
         <v>2.0</v>
@@ -1452,7 +1482,7 @@
       <c r="J9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L9" s="5"/>
@@ -1472,26 +1502,26 @@
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
     </row>
-    <row r="10" ht="30.75" customHeight="1">
+    <row r="10" ht="53.25" customHeight="1">
       <c r="A10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="E10" s="25" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>50</v>
       </c>
       <c r="F10" s="22">
         <v>8.0</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="19">
         <v>5.0</v>
       </c>
       <c r="H10" s="25">
@@ -1503,7 +1533,7 @@
       <c r="J10" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L10" s="5"/>
@@ -1523,27 +1553,27 @@
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
     </row>
-    <row r="11" ht="40.5" customHeight="1">
+    <row r="11" ht="30.75" customHeight="1">
       <c r="A11" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="E11" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>53</v>
+      <c r="F11" s="22">
+        <v>8.0</v>
       </c>
-      <c r="D11" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="25">
-        <v>3.0</v>
-      </c>
-      <c r="G11" s="25">
-        <v>2.0</v>
+      <c r="G11" s="18">
+        <v>5.0</v>
       </c>
       <c r="H11" s="25">
         <v>2.0</v>
@@ -1551,10 +1581,10 @@
       <c r="I11" s="25">
         <v>2.0</v>
       </c>
-      <c r="J11" s="25" t="s">
-        <v>35</v>
+      <c r="J11" s="22" t="s">
+        <v>16</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="11" t="s">
         <v>17</v>
       </c>
       <c r="L11" s="5"/>
@@ -1574,18 +1604,40 @@
       <c r="Z11" s="5"/>
       <c r="AA11" s="5"/>
     </row>
-    <row r="12" ht="44.25" customHeight="1">
-      <c r="A12" s="27"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
+    <row r="12" ht="40.5" customHeight="1">
+      <c r="A12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="G12" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="H12" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="I12" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
@@ -1604,17 +1656,37 @@
       <c r="AA12" s="5"/>
     </row>
     <row r="13" ht="40.5" customHeight="1">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
+      <c r="A13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="20"/>
+      <c r="F13" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="G13" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="H13" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="I13" s="25">
+        <v>3.0</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
@@ -1632,13 +1704,16 @@
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
     </row>
-    <row r="14" ht="63.0" customHeight="1">
-      <c r="A14" s="28"/>
+    <row r="14" ht="44.25" customHeight="1">
+      <c r="A14" s="27"/>
       <c r="B14" s="28"/>
       <c r="C14" s="29"/>
       <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
       <c r="F14" s="31"/>
       <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="31"/>
       <c r="K14" s="31"/>
       <c r="L14" s="5"/>
@@ -1658,13 +1733,16 @@
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
     </row>
-    <row r="15" ht="54.75" customHeight="1">
-      <c r="A15" s="28"/>
+    <row r="15" ht="44.25" customHeight="1">
+      <c r="A15" s="27"/>
       <c r="B15" s="28"/>
       <c r="C15" s="29"/>
       <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
       <c r="F15" s="31"/>
       <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
       <c r="J15" s="31"/>
       <c r="K15" s="31"/>
       <c r="L15" s="5"/>
@@ -1684,13 +1762,16 @@
       <c r="Z15" s="5"/>
       <c r="AA15" s="5"/>
     </row>
-    <row r="16" ht="48.0" customHeight="1">
+    <row r="16" ht="40.5" customHeight="1">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="29"/>
       <c r="D16" s="30"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="31"/>
       <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
       <c r="J16" s="31"/>
       <c r="K16" s="31"/>
       <c r="L16" s="5"/>
@@ -1710,16 +1791,13 @@
       <c r="Z16" s="5"/>
       <c r="AA16" s="5"/>
     </row>
-    <row r="17" ht="48.0" customHeight="1">
+    <row r="17" ht="63.0" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
-      <c r="C17" s="31"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="30"/>
-      <c r="E17" s="32"/>
       <c r="F17" s="31"/>
       <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
       <c r="J17" s="31"/>
       <c r="K17" s="31"/>
       <c r="L17" s="5"/>
@@ -1739,10 +1817,10 @@
       <c r="Z17" s="5"/>
       <c r="AA17" s="5"/>
     </row>
-    <row r="18" ht="47.25" customHeight="1">
+    <row r="18" ht="54.75" customHeight="1">
       <c r="A18" s="28"/>
       <c r="B18" s="28"/>
-      <c r="C18" s="31"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="30"/>
       <c r="F18" s="31"/>
       <c r="G18" s="31"/>
@@ -1765,10 +1843,10 @@
       <c r="Z18" s="5"/>
       <c r="AA18" s="5"/>
     </row>
-    <row r="19" ht="51.0" customHeight="1">
+    <row r="19" ht="48.0" customHeight="1">
       <c r="A19" s="28"/>
       <c r="B19" s="28"/>
-      <c r="C19" s="31"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="30"/>
       <c r="F19" s="31"/>
       <c r="G19" s="31"/>
@@ -1791,13 +1869,16 @@
       <c r="Z19" s="5"/>
       <c r="AA19" s="5"/>
     </row>
-    <row r="20" ht="51.75" customHeight="1">
+    <row r="20" ht="48.0" customHeight="1">
       <c r="A20" s="28"/>
       <c r="B20" s="28"/>
       <c r="C20" s="31"/>
       <c r="D20" s="30"/>
+      <c r="E20" s="32"/>
       <c r="F20" s="31"/>
       <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
       <c r="J20" s="31"/>
       <c r="K20" s="31"/>
       <c r="L20" s="5"/>
@@ -1817,18 +1898,15 @@
       <c r="Z20" s="5"/>
       <c r="AA20" s="5"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="5"/>
+    <row r="21" ht="47.25" customHeight="1">
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
@@ -1846,18 +1924,15 @@
       <c r="Z21" s="5"/>
       <c r="AA21" s="5"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="33"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="5"/>
+    <row r="22" ht="51.0" customHeight="1">
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -1875,18 +1950,15 @@
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="33"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="5"/>
+    <row r="23" ht="51.75" customHeight="1">
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -1909,11 +1981,11 @@
       <c r="B24" s="5"/>
       <c r="C24" s="34"/>
       <c r="D24" s="35"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
       <c r="J24" s="37"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -1934,16 +2006,16 @@
       <c r="AA24" s="5"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5"/>
+      <c r="A25" s="33"/>
       <c r="B25" s="5"/>
       <c r="C25" s="34"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="37"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
@@ -1963,16 +2035,16 @@
       <c r="AA25" s="5"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5"/>
+      <c r="A26" s="33"/>
       <c r="B26" s="5"/>
       <c r="C26" s="34"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="37"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
@@ -1992,16 +2064,16 @@
       <c r="AA26" s="5"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5"/>
+      <c r="A27" s="33"/>
       <c r="B27" s="5"/>
       <c r="C27" s="34"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="37"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
@@ -2138,8 +2210,8 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="5"/>
-      <c r="B32" s="40"/>
-      <c r="C32" s="38"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="34"/>
       <c r="D32" s="39"/>
       <c r="E32" s="32"/>
       <c r="F32" s="32"/>
@@ -2167,8 +2239,8 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="38"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="34"/>
       <c r="D33" s="39"/>
       <c r="E33" s="32"/>
       <c r="F33" s="32"/>
@@ -2196,8 +2268,8 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="5"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="38"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="34"/>
       <c r="D34" s="39"/>
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
@@ -2399,8 +2471,8 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="34"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="38"/>
       <c r="D41" s="39"/>
       <c r="E41" s="32"/>
       <c r="F41" s="32"/>
@@ -2428,8 +2500,8 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="34"/>
+      <c r="B42" s="40"/>
+      <c r="C42" s="38"/>
       <c r="D42" s="39"/>
       <c r="E42" s="32"/>
       <c r="F42" s="32"/>
@@ -2457,8 +2529,8 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="34"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="38"/>
       <c r="D43" s="39"/>
       <c r="E43" s="32"/>
       <c r="F43" s="32"/>
@@ -7621,13 +7693,13 @@
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="34"/>
-      <c r="D221" s="41"/>
-      <c r="E221" s="5"/>
-      <c r="F221" s="5"/>
-      <c r="G221" s="5"/>
-      <c r="H221" s="5"/>
-      <c r="I221" s="5"/>
-      <c r="J221" s="5"/>
+      <c r="D221" s="39"/>
+      <c r="E221" s="32"/>
+      <c r="F221" s="32"/>
+      <c r="G221" s="32"/>
+      <c r="H221" s="32"/>
+      <c r="I221" s="32"/>
+      <c r="J221" s="32"/>
       <c r="K221" s="5"/>
       <c r="L221" s="5"/>
       <c r="M221" s="5"/>
@@ -7650,13 +7722,13 @@
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="34"/>
-      <c r="D222" s="41"/>
-      <c r="E222" s="5"/>
-      <c r="F222" s="5"/>
-      <c r="G222" s="5"/>
-      <c r="H222" s="5"/>
-      <c r="I222" s="5"/>
-      <c r="J222" s="5"/>
+      <c r="D222" s="39"/>
+      <c r="E222" s="32"/>
+      <c r="F222" s="32"/>
+      <c r="G222" s="32"/>
+      <c r="H222" s="32"/>
+      <c r="I222" s="32"/>
+      <c r="J222" s="32"/>
       <c r="K222" s="5"/>
       <c r="L222" s="5"/>
       <c r="M222" s="5"/>
@@ -7679,13 +7751,13 @@
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="34"/>
-      <c r="D223" s="41"/>
-      <c r="E223" s="5"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="5"/>
-      <c r="H223" s="5"/>
-      <c r="I223" s="5"/>
-      <c r="J223" s="5"/>
+      <c r="D223" s="39"/>
+      <c r="E223" s="32"/>
+      <c r="F223" s="32"/>
+      <c r="G223" s="32"/>
+      <c r="H223" s="32"/>
+      <c r="I223" s="32"/>
+      <c r="J223" s="32"/>
       <c r="K223" s="5"/>
       <c r="L223" s="5"/>
       <c r="M223" s="5"/>
@@ -30034,7 +30106,7 @@
       <c r="Z993" s="5"/>
       <c r="AA993" s="5"/>
     </row>
-    <row r="994">
+    <row r="994" ht="15.75" customHeight="1">
       <c r="A994" s="5"/>
       <c r="B994" s="5"/>
       <c r="C994" s="34"/>
@@ -30063,7 +30135,7 @@
       <c r="Z994" s="5"/>
       <c r="AA994" s="5"/>
     </row>
-    <row r="995">
+    <row r="995" ht="15.75" customHeight="1">
       <c r="A995" s="5"/>
       <c r="B995" s="5"/>
       <c r="C995" s="34"/>
@@ -30092,7 +30164,7 @@
       <c r="Z995" s="5"/>
       <c r="AA995" s="5"/>
     </row>
-    <row r="996">
+    <row r="996" ht="15.75" customHeight="1">
       <c r="A996" s="5"/>
       <c r="B996" s="5"/>
       <c r="C996" s="34"/>
@@ -30324,22 +30396,113 @@
       <c r="Z1003" s="5"/>
       <c r="AA1003" s="5"/>
     </row>
+    <row r="1004">
+      <c r="A1004" s="5"/>
+      <c r="B1004" s="5"/>
+      <c r="C1004" s="34"/>
+      <c r="D1004" s="41"/>
+      <c r="E1004" s="5"/>
+      <c r="F1004" s="5"/>
+      <c r="G1004" s="5"/>
+      <c r="H1004" s="5"/>
+      <c r="I1004" s="5"/>
+      <c r="J1004" s="5"/>
+      <c r="K1004" s="5"/>
+      <c r="L1004" s="5"/>
+      <c r="M1004" s="5"/>
+      <c r="N1004" s="5"/>
+      <c r="O1004" s="5"/>
+      <c r="P1004" s="5"/>
+      <c r="Q1004" s="5"/>
+      <c r="R1004" s="5"/>
+      <c r="S1004" s="5"/>
+      <c r="T1004" s="5"/>
+      <c r="U1004" s="5"/>
+      <c r="V1004" s="5"/>
+      <c r="W1004" s="5"/>
+      <c r="X1004" s="5"/>
+      <c r="Y1004" s="5"/>
+      <c r="Z1004" s="5"/>
+      <c r="AA1004" s="5"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="5"/>
+      <c r="B1005" s="5"/>
+      <c r="C1005" s="34"/>
+      <c r="D1005" s="41"/>
+      <c r="E1005" s="5"/>
+      <c r="F1005" s="5"/>
+      <c r="G1005" s="5"/>
+      <c r="H1005" s="5"/>
+      <c r="I1005" s="5"/>
+      <c r="J1005" s="5"/>
+      <c r="K1005" s="5"/>
+      <c r="L1005" s="5"/>
+      <c r="M1005" s="5"/>
+      <c r="N1005" s="5"/>
+      <c r="O1005" s="5"/>
+      <c r="P1005" s="5"/>
+      <c r="Q1005" s="5"/>
+      <c r="R1005" s="5"/>
+      <c r="S1005" s="5"/>
+      <c r="T1005" s="5"/>
+      <c r="U1005" s="5"/>
+      <c r="V1005" s="5"/>
+      <c r="W1005" s="5"/>
+      <c r="X1005" s="5"/>
+      <c r="Y1005" s="5"/>
+      <c r="Z1005" s="5"/>
+      <c r="AA1005" s="5"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="5"/>
+      <c r="B1006" s="5"/>
+      <c r="C1006" s="34"/>
+      <c r="D1006" s="41"/>
+      <c r="E1006" s="5"/>
+      <c r="F1006" s="5"/>
+      <c r="G1006" s="5"/>
+      <c r="H1006" s="5"/>
+      <c r="I1006" s="5"/>
+      <c r="J1006" s="5"/>
+      <c r="K1006" s="5"/>
+      <c r="L1006" s="5"/>
+      <c r="M1006" s="5"/>
+      <c r="N1006" s="5"/>
+      <c r="O1006" s="5"/>
+      <c r="P1006" s="5"/>
+      <c r="Q1006" s="5"/>
+      <c r="R1006" s="5"/>
+      <c r="S1006" s="5"/>
+      <c r="T1006" s="5"/>
+      <c r="U1006" s="5"/>
+      <c r="V1006" s="5"/>
+      <c r="W1006" s="5"/>
+      <c r="X1006" s="5"/>
+      <c r="Y1006" s="5"/>
+      <c r="Z1006" s="5"/>
+      <c r="AA1006" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E13:E16"/>
-    <mergeCell ref="H13:H16"/>
-    <mergeCell ref="I13:I16"/>
-    <mergeCell ref="E17:E20"/>
-    <mergeCell ref="H17:H20"/>
-    <mergeCell ref="I17:I20"/>
-    <mergeCell ref="E6:E8"/>
+  <mergeCells count="10">
+    <mergeCell ref="H20:H23"/>
+    <mergeCell ref="I20:I23"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E16:E19"/>
+    <mergeCell ref="H16:H19"/>
+    <mergeCell ref="I16:I19"/>
+    <mergeCell ref="E20:E23"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="E12:E13"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="D13"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -30355,7 +30518,7 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="G1" s="42" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
